--- a/docs/product_backlog/product backlog template.xlsx
+++ b/docs/product_backlog/product backlog template.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A7F7B4D-5D7C-4DF7-B1F1-EE1BF93513F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC266036-F164-447E-8A2D-849A02AD8F39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10714" yWindow="0" windowWidth="10972" windowHeight="13766" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="21806" windowHeight="13886" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="103">
   <si>
     <t>Story ID</t>
   </si>
@@ -329,6 +329,94 @@
   </si>
   <si>
     <t>AI Feature</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AD-01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Check TA Overall Workload</t>
+  </si>
+  <si>
+    <t>As an Admin, I want to check TAs' overall workload across all modules, So that I can identify if any single TA has taken on excessive positions.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. Dashboard lists all TAs and their total assigned hours/modules.
+2. Visually flags TAs who exceed workload limits.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AD-02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AD-03</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AD-04</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AD-05</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Global Vacancy Dashboard</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Manage Overloaded Tas</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Export Final Hiring List</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI Workload Balancing</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>As an Admin, I want a global overview of which modules are still unfilled, So that I can monitor university-wide recruitment progress.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>As an Admin, I want to force dismiss or transfer positions for overloaded TAs, So that I can enforce workload limits and resolve conflicts.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>As an Admin, I want to quickly export the final hiring list, So that I can process data reports and administrative tasks.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>As an Admin, I want the AI to intelligently analyze allocations and provide workload balancing suggestions, So that I can optimally distribute TA resources.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. Dashboard lists all modules.
+2. Displays required TA headcount for each module.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. Admin can manually remove a TA from a specific module
+2. System instantly updates module vacancy and TA workload.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. Provide a "One-click Export" button.
+2. Generates CSV/Excel with confirmed TA allocations.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. AI detects imbalanced distributions across modules
+2. System suggests moving specific TAs to balance hours.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Admin Survey</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -739,7 +827,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr defaultColWidth="8.84375" defaultRowHeight="14.15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.921875" style="1" bestFit="1" customWidth="1"/>
@@ -1282,6 +1370,136 @@
         <v>81</v>
       </c>
     </row>
+    <row r="18" spans="1:8" ht="99" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B18" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" s="1">
+        <v>1</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G18" s="1">
+        <v>5</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="84.9" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" s="1">
+        <v>2</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G19" s="1">
+        <v>3</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="99" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E20" s="1">
+        <v>4</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G20" s="1">
+        <v>3</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="84.9" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E21" s="1">
+        <v>2</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="G21" s="1">
+        <v>2</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="113.15" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E22" s="1">
+        <v>3</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G22" s="1">
+        <v>5</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
